--- a/Lasser_Driver_v5/pm22V/pm22V_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/pm22V/pm22V_BOM_digikey_priced.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C1,C2</t>
+          <t>pm22V C1,C2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C3,C4,C9,C10</t>
+          <t>pm22V C3,C4,C9,C10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C5,C6</t>
+          <t>pm22V C5,C6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C7,C8</t>
+          <t>pm22V C7,C8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -835,46 +835,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPC1510-E4/51</t>
+          <t>GBPC1510W</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Surge Components</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>pm22V D1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GBPC1510</t>
+          <t>GBPC1510W (GBPC-W)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diode_Bridge_GBPC</t>
+          <t>Diode_Bridge_GBPC-W_PCB</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bridge rect 15A 1000V GBPC bolt</t>
+          <t>Bridge rect 15A 1000V GBPC-W wire-lead PCB+bolt</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>GBPC1510-E4/51-ND</t>
+          <t>2616-GBPC1510W-ND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vishay General Semiconductor - Diodes Division</t>
+          <t>SURGE</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>7.88</v>
+        <v>2.24</v>
       </c>
       <c r="O6" s="2">
         <f>N6*L6</f>
@@ -896,10 +896,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://www.vishay.com/docs/88612/gbpc12.pdf</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/3003/GBPC15.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>APPROX MATCH -&gt; GBPC1510W (verify)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -917,7 +921,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D2,D3</t>
+          <t>pm22V D2,D3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HS1,HS2</t>
+          <t>pm22V HS1,HS2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1061,7 +1065,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HS3</t>
+          <t>pm22V HS3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q1,Q2 (TO-220 iso)</t>
+          <t>pm22V Q1,Q2 (TO-220 iso)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1195,46 +1199,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1757255</t>
+          <t>TG-A3500-30-30-0.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix Contact</t>
+          <t>t-Global</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>pm22V D1/HS3 (thermal)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MSTBA 2,5/3-G-5,08</t>
+          <t>30x30x0.5mm pad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phoenix_MSTBA_3</t>
+          <t>Hardware (off-PCB)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Term block header 3pos 5.08mm horiz</t>
+          <t>Thermal pad 30x30x0.5mm for GBPC bridge to HS3</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>277-1107-ND</t>
+          <t>1168-TG-A3500-30-30-0.5-ND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Phoenix Contact</t>
+          <t>t-Global Technology</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11325</v>
+        <v>2058</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1248,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="2">
         <f>N11*L11</f>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://www.phoenixcontact.com/us/products/1757255/pdf</t>
+          <t>https://www.tglobaltechnology.com/wp-content/uploads/2023/08/TG-A3500_UK.pdf</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1267,46 +1271,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>374144-E</t>
+          <t>1729131</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TE/ERNI</t>
+          <t>Phoenix Contact</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>J6</t>
+          <t>pm22V J5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DIN41612 M 3x8+8</t>
+          <t>MKDS 1,5/3-5,08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DIN41612_M_Power_Male</t>
+          <t>TerminalBlock_MKDS_3_P5.08mm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIN41612 Type M 24sig+8pwr R/A male</t>
+          <t>Single-piece PCB screw terminal 3pos 5.08mm side-entry</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2684-374144-E-ND</t>
+          <t>277-1248-ND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TE Connectivity Erni</t>
+          <t>Phoenix Contact</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>15236</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1320,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>10.31</v>
+        <v>1.44</v>
       </c>
       <c r="O12" s="2">
         <f>N12*L12</f>
@@ -1328,14 +1332,10 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://www.erni.com/fileadmin/import/products/assets/DC0006731.PDF</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>LOW STOCK (0 &lt; 1)</t>
-        </is>
-      </c>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/5784/MKDSN%201%2C5_%203-5%2C08.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1343,46 +1343,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IRF540NPBF</t>
+          <t>374144-E</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>TE/ERNI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>pm22V J6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IRF540N</t>
+          <t>DIN41612 M 3x8+8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TO-220-3</t>
+          <t>DIN41612_M_Power_Male</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>N-MOSFET 100V 33A TO-220 (pos pass)</t>
+          <t>DIN41612 Type M 24sig+8pwr R/A male</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>IRF540NPBF-ND</t>
+          <t>2684-374144-E-ND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>TE Connectivity Erni</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.93</v>
+        <v>10.31</v>
       </c>
       <c r="O13" s="2">
         <f>N13*L13</f>
@@ -1404,10 +1404,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf540n-datasheet-en.pdf</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+          <t>https://www.erni.com/fileadmin/import/products/assets/DC0006731.PDF</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>LOW STOCK (0 &lt; 1)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1415,7 +1419,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IRF9540NPBF</t>
+          <t>IRF540NPBF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1425,12 +1429,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>pm22V Q1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IRF9540N</t>
+          <t>IRF540N</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1440,12 +1444,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P-MOSFET -100V TO-220 (neg pass)</t>
+          <t>N-MOSFET 100V 33A TO-220 (pos pass)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IRF9540NPBF-ND</t>
+          <t>IRF540NPBF-ND</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1454,7 +1458,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12195</v>
+        <v>64</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1468,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.91</v>
+        <v>1.93</v>
       </c>
       <c r="O14" s="2">
         <f>N14*L14</f>
@@ -1476,57 +1480,57 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf9540n-datasheet-en.pdf</t>
+          <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf540n-datasheet-en.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TUW15J15RE</t>
+          <t>IRF9540NPBF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ohmite</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R2,R3</t>
+          <t>pm22V Q2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15 ohm 15W</t>
+          <t>IRF9540N</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R_Axial_Power_P45.72mm</t>
+          <t>TO-220-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>WW 15ohm 15W axial (soft-start)</t>
+          <t>P-MOSFET -100V TO-220 (neg pass)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TUW15J15RE-ND</t>
+          <t>IRF9540NPBF-ND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ohmite</t>
+          <t>Infineon Technologies</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3814</v>
+        <v>12195</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1534,13 +1538,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.07</v>
+        <v>2.91</v>
       </c>
       <c r="O15" s="2">
         <f>N15*L15</f>
@@ -1548,7 +1552,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://www.ohmite.com/assets/images/res-tuw-tum.pdf</t>
+          <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf9540n-datasheet-en.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1559,46 +1563,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RC0805FR-071ML</t>
+          <t>TUW15J15RE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Ohmite</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R4,R5</t>
+          <t>pm22V R2,R3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>15 ohm 15W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R_0805</t>
+          <t>R_Axial_Power_P45.72mm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Res 1M 1% 1/8W 0805 (gate bleed)</t>
+          <t>WW 15ohm 15W axial (soft-start)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>311-1.00MCRTR-ND</t>
+          <t>TUW15J15RE-ND</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Ohmite</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>318676</v>
+        <v>3814</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1612,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1</v>
+        <v>2.07</v>
       </c>
       <c r="O16" s="2">
         <f>N16*L16</f>
@@ -1620,7 +1624,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
+          <t>https://www.ohmite.com/assets/images/res-tuw-tum.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -1631,7 +1635,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RC0805FR-07100KL</t>
+          <t>RC0805FR-071ML</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R6,R7</t>
+          <t>pm22V R4,R5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1656,12 +1660,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Res 100k 1% 1/8W 0805 (gate pull)</t>
+          <t>Res 1M 1% 1/8W 0805 (gate bleed)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>311-100KCRTR-ND</t>
+          <t>311-1.00MCRTR-ND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1670,7 +1674,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>633017</v>
+        <v>318676</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1703,46 +1707,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CRL1206-FW-R470ELF</t>
+          <t>RC0805FR-07100KL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R8,R9</t>
+          <t>pm22V R6,R7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R_1206</t>
+          <t>R_0805</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Res 0.47ohm 1% 1/2W 1206 (output series)</t>
+          <t>Res 100k 1% 1/8W 0805 (gate pull)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>118-CRL1206-FW-R470ELFTR-ND</t>
+          <t>311-100KCRTR-ND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Bourns Inc.</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48005</v>
+        <v>633012</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1756,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="2">
         <f>N18*L18</f>
@@ -1764,30 +1768,102 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CRL1206-FW-R470ELF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bourns</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pm22V R8,R9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R_1206</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Res 0.47ohm 1% 1/2W 1206 (output series)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>118-CRL1206-FW-R470ELFTR-ND</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bourns Inc.</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>48005</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O19" s="2">
+        <f>N19*L19</f>
+        <v/>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>https://www.bourns.com/docs/Product-Datasheets/CRL.pdf</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="O20" s="3">
-        <f>SUM(O2:O18)</f>
+      <c r="O21" s="3">
+        <f>SUM(O2:O19)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Prices pulled 2026-06-30 14:34 (USD), 1 board(s)</t>
+    <row r="22">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Prices pulled 2026-06-30 15:06 (USD), 1 board(s)</t>
         </is>
       </c>
     </row>
